--- a/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
+++ b/jpcore-r4/feature/swg2-dental-eCS/StructureDefinition-jp-observation-dentaloral-bodystructure.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="238" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="370" uniqueCount="133">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-30</t>
+    <t>2025-06-24</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -349,6 +349,80 @@
   <si>
     <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
+  </si>
+  <si>
+    <t>Extension.value[x].id</t>
+  </si>
+  <si>
+    <t>Extension.value[x].extension</t>
+  </si>
+  <si>
+    <t>extensions
+user content</t>
+  </si>
+  <si>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>Extension.value[x].coding</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコード / Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>用語システムによって定義されたコードへの参照。 / A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>コードは、列挙されたCTなどの非常に正式な定義まで、列挙またはコードリストで非常にさりげなく定義される場合があります。詳細については、HL7 V3コアプリンシップを参照してください。コーディングの順序付けは未定義であり、意味を推測するために使用されません。一般に、せいぜい、コーディング値の1つのみがuserselected = trueとしてラベル付けされます。 / Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>コードシステム内の代替エンコーディング、および他のコードシステムへの翻訳が可能になります。 / Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>preferred</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/ValueSet/JP_DentalBodyStructure_VS</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Extension.value[x].text</t>
+  </si>
+  <si>
+    <t>コンセプトの単純なテキスト表現 / Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>データを入力したユーザー、および/またはユーザーの意図された意味を表すユーザーによって見られる/選択/発言された概念の人間の言語表現。 / A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>多くの場合、テキストはコーディングの1つの表示名と同じです。 / Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>用語からのコードは、それらを使用する人間のすべてのニュアンスを使用して、常に正しい意味をキャプチャするとは限りません。または、適切なコードがまったくない場合があります。これらの場合、テキストはソースの完全な意味をキャプチャするために使用されます。 / The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
 </sst>
 </file>
@@ -660,13 +734,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK6"/>
+  <dimension ref="A1:AK10"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="16.80078125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="16.80078125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="23.75" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="23.75" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="7.6796875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="10.83984375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
     <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
@@ -677,7 +751,7 @@
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
-    <col min="15" max="15" width="13.4296875" customWidth="true" bestFit="true"/>
+    <col min="15" max="15" width="255.0" customWidth="true" bestFit="true"/>
     <col min="16" max="16" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
@@ -688,17 +762,17 @@
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="18.49609375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="16.828125" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="48.48046875" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="15.59375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="20.5390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="21.4140625" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="39.890625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1331,6 +1405,426 @@
         <v>103</v>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="B7" t="s" s="2">
+        <v>109</v>
+      </c>
+      <c r="C7" s="2"/>
+      <c r="D7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E7" s="2"/>
+      <c r="F7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K7" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L7" t="s" s="2">
+        <v>87</v>
+      </c>
+      <c r="M7" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="N7" s="2"/>
+      <c r="O7" s="2"/>
+      <c r="P7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q7" s="2"/>
+      <c r="R7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF7" t="s" s="2">
+        <v>89</v>
+      </c>
+      <c r="AG7" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH7" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ7" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AK7" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="B8" t="s" s="2">
+        <v>110</v>
+      </c>
+      <c r="C8" s="2"/>
+      <c r="D8" t="s" s="2">
+        <v>111</v>
+      </c>
+      <c r="E8" s="2"/>
+      <c r="F8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="K8" t="s" s="2">
+        <v>92</v>
+      </c>
+      <c r="L8" t="s" s="2">
+        <v>112</v>
+      </c>
+      <c r="M8" t="s" s="2">
+        <v>113</v>
+      </c>
+      <c r="N8" t="s" s="2">
+        <v>114</v>
+      </c>
+      <c r="O8" s="2"/>
+      <c r="P8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q8" s="2"/>
+      <c r="R8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB8" t="s" s="2">
+        <v>94</v>
+      </c>
+      <c r="AC8" t="s" s="2">
+        <v>95</v>
+      </c>
+      <c r="AD8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE8" t="s" s="2">
+        <v>96</v>
+      </c>
+      <c r="AF8" t="s" s="2">
+        <v>97</v>
+      </c>
+      <c r="AG8" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH8" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI8" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ8" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AK8" t="s" s="2">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="B9" t="s" s="2">
+        <v>115</v>
+      </c>
+      <c r="C9" s="2"/>
+      <c r="D9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E9" s="2"/>
+      <c r="F9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="H9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J9" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="K9" t="s" s="2">
+        <v>117</v>
+      </c>
+      <c r="L9" t="s" s="2">
+        <v>118</v>
+      </c>
+      <c r="M9" t="s" s="2">
+        <v>119</v>
+      </c>
+      <c r="N9" t="s" s="2">
+        <v>120</v>
+      </c>
+      <c r="O9" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="P9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q9" s="2"/>
+      <c r="R9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X9" t="s" s="2">
+        <v>122</v>
+      </c>
+      <c r="Y9" s="2"/>
+      <c r="Z9" t="s" s="2">
+        <v>123</v>
+      </c>
+      <c r="AA9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF9" t="s" s="2">
+        <v>124</v>
+      </c>
+      <c r="AG9" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH9" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AI9" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ9" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK9" t="s" s="2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="B10" t="s" s="2">
+        <v>126</v>
+      </c>
+      <c r="C10" s="2"/>
+      <c r="D10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="E10" s="2"/>
+      <c r="F10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="G10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="H10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="I10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="J10" t="s" s="2">
+        <v>116</v>
+      </c>
+      <c r="K10" t="s" s="2">
+        <v>86</v>
+      </c>
+      <c r="L10" t="s" s="2">
+        <v>127</v>
+      </c>
+      <c r="M10" t="s" s="2">
+        <v>128</v>
+      </c>
+      <c r="N10" t="s" s="2">
+        <v>129</v>
+      </c>
+      <c r="O10" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="P10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Q10" s="2"/>
+      <c r="R10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="S10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="T10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="U10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="V10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="W10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="X10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Y10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="Z10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AA10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AB10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AC10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AD10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AE10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AF10" t="s" s="2">
+        <v>131</v>
+      </c>
+      <c r="AG10" t="s" s="2">
+        <v>78</v>
+      </c>
+      <c r="AH10" t="s" s="2">
+        <v>85</v>
+      </c>
+      <c r="AI10" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ10" t="s" s="2">
+        <v>108</v>
+      </c>
+      <c r="AK10" t="s" s="2">
+        <v>132</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
